--- a/data/trans_orig/P6907S1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6907S1-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76219</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26469</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95799</t>
+          <t>95372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107344</t>
+          <t>107597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33887</t>
+          <t>36397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119041</t>
+          <t>119030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136361</t>
+          <t>136664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40717</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49986</t>
+          <t>50647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164890</t>
+          <t>162380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184364</t>
+          <t>183667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93112</t>
+          <t>92670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106908</t>
+          <t>106132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>37695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135235</t>
+          <t>135040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150024</t>
+          <t>150063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>32221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119809</t>
+          <t>119274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130773</t>
+          <t>131125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69780</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82410</t>
+          <t>82176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>193091</t>
+          <t>193379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210491</t>
+          <t>210794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>84594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415022</t>
+          <t>414413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>440931</t>
+          <t>440013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185823</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203976</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>607833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>640204</t>
+          <t>640300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012 (tasa de respuesta: 44,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>27212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>33554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44611</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51354</t>
+          <t>51359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,62 +3058,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6276</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6118</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52680</t>
+          <t>52522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35918</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27059</t>
+          <t>24844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65394</t>
+          <t>65337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72255</t>
+          <t>72258</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51292</t>
+          <t>51821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57715</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128713</t>
+          <t>127469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138749</t>
+          <t>138869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92422</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99260</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224361</t>
+          <t>223952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>237048</t>
+          <t>237271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48427</t>
+          <t>48421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76991</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88493</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95995</t>
+          <t>95988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46399</t>
+          <t>47084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54611</t>
+          <t>54628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139021</t>
+          <t>139251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149672</t>
+          <t>150439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101835</t>
+          <t>101274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109014</t>
+          <t>109000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166130</t>
+          <t>165828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173753</t>
+          <t>173752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78320</t>
+          <t>78336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86621</t>
+          <t>86632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>60586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142482</t>
+          <t>142500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152481</t>
+          <t>152390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328911</t>
+          <t>329642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343179</t>
+          <t>343846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204528</t>
+          <t>203460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214425</t>
+          <t>214384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>539343</t>
+          <t>537290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>555555</t>
+          <t>555834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52005</t>
+          <t>51643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66803</t>
+          <t>66731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50742</t>
+          <t>50582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103956</t>
+          <t>104332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120641</t>
+          <t>120687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>28909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88956</t>
+          <t>89045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103744</t>
+          <t>104075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88413</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96167</t>
+          <t>96057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180966</t>
+          <t>181803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197792</t>
+          <t>198746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28827</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44827</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>53767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73471</t>
+          <t>73786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93172</t>
+          <t>93467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123357</t>
+          <t>124233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144645</t>
+          <t>144828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85450</t>
+          <t>86114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86915</t>
+          <t>87385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98586</t>
+          <t>98515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178271</t>
+          <t>178720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193507</t>
+          <t>193452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83611</t>
+          <t>84552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>288211</t>
+          <t>287728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>312746</t>
+          <t>313145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313160</t>
+          <t>312508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>335022</t>
+          <t>334800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>610109</t>
+          <t>609168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>644243</t>
+          <t>643500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
